--- a/cronograma_nr_alimentação_30_12_2025.xlsx
+++ b/cronograma_nr_alimentação_30_12_2025.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -510,12 +510,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>31/12/2025 07:00</t>
+          <t>31/12/2025 00:00</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>43/2025</t>
+          <t>006/2024</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -525,93 +525,93 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE AUGUSTO DE LIMA</t>
+          <t>MUNICIPIO DE DORES DE GUANHAES</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>AQUISICAO DE GENEROS ALIMENTICIOS ATRAVES DA AGRICULTURA FAMILIAR PARA ALIMENTACAO ESCOLAR DA REDE DE EDUCACAO BASICA PUBICA DO MUNICIPIO, EM ATENDIMENTO AO PROGRAMA NACIONAL DE ALIMENTACAO ESCOLAR  PNAEFNDE.</t>
+          <t>[LICITANET] - LOCAÇÃO MENSAL DE VEICULO TIPO PASSEIO MOTOR MÍNIMO DE 1.0 (COM MOTORISTA POR CONTA DA CONTRATADA E COMBUSTÍVEL POR CONTA DA CONTRATANTE, PARA TRANSPORTE DE PESSOAL URBANO, LOCAÇÃO MENSAL DE VEÍCULO TIPO PASSEIO MOTOR MÍNIMO DE 1.0 (COM MOTORISTA POR CONTA DA CONTRATADA E COMBUSTÍVEL POR CONTA DA CONTRATANTE); COM CAPACIDADE PARA 05 (CINCO) PESSOAS, AIRBAG, COM AR CONDICIONADO, DIREÇÃO HIDRÁULICA OU ELÉTRICA, VIDRO ELÉTRICO (MÍNIMO NAS DUAS PORTAS DIANTEIRAS), TRAVAS ELÉTRICAS NAS QUATRO PORTAS, BICOMBUSTÍVEL (GASOLINA E ETANOL), 04 PORTAS. CONTROLE DE TRAÇÃO E ESTABILIDADE. O(S) VEÍCULO(S) DEVERÃO SER EMPLACADOS E REGULARIZADOS JUNTO AOS ÓRGÃOS DE TRÂNSITO. QUILOMETRAGEM LIVRE, MANUTENÇÃO PREVENTIVA E CORRETIVA COM REPOSIÇÃO DE PEÇAS. IPVA, MANUTENÇÃO, LICENCIAMENTO, SEGURO TOTAL, FRANQUIA E DEMAIS TAXAS POR CONTA DA CONTRATADA, COM NO MÁXIMO 02 (DOIS) ANOS DE FABRICAÇÃO, ANTERIOR À DATA DA CONTRATAÇÃO, CORES BRANCAS, CINZA OU PRATA.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>1687</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>31/12/2025 07:00</t>
+          <t>31/12/2025 08:00</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>30/2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Dispensa</t>
+          <t>19/2025</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Credenciamento</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE AUGUSTO DE LIMA</t>
+          <t>MUNICIPIO DE DOM JOAQUIM</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>AQUISICAO DE GENEROS ALIMENTICIOS: PAES, ROSCAS, TORTAS, PASTEL, BOLO, BISCOITOS, COXINHA, EMPADA, SANDUICHE, E  ATENDIMENTOS  AOS  SERVIDORES PUBLICOS MUNICIPAIS, CONFORME CONDICOES E ESPECIFICACOES CONSTANTES DFD E TERMO REFERENCIA.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇO DE INSTALAÇÃO, MANUTENÇÃO PREVENTIVA/CORRETIVA, CALIBRAÇÃO DOS EQUIPAMENTOS COM REPOSIÇÃO DE PEÇAS, ACESSÓRIOS OU SUBSTITUIÇÃO DE EQUIPAMENTOS NECESSÁRIOS À RECEPÇÃO E RETRANSMISSÃO DE SINAL DE TV E MELHORIA DO SISTEMA DE RTV ANALÓGICO E DIGITAL, EXISTENTE NO MUNICÍPIO DE DOM JOAQUIM-MG.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>021101</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>31/12/2025 09:00</t>
+          <t>31/12/2025 08:00</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>29/2025</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Dispensa</t>
+          <t>103/2025</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Credenciamento</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE PEDRAS DE MARIA DA CRUZ</t>
+          <t>MUNICIPIO DE CORONEL PACHECO</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>AQUISICAO DE GENEROS ALIMENTICIOS DA AGRICULTURA FAMILIAR E DO EMPREENDEDOR FAMILIAR RURAL, PARA O ATENDIMENTO AO PROGRAMA NACIONAL DE ALIMENTACAO ESCOLAR  PNAE, PARA ATENDER AS NECESSIDADES DA ALIMENTACAO ESCOLAR DO MUNICIPIO DE PEDRAS DE MARIA DA CRUZ, MG.</t>
+          <t>CREDENCIAMENTO DE EMPRESAS ESPECIALIZADAS NA PRESTAÇÃO DE SERVIÇOS MECÂNICOS EM GERAL MANUTENÇÃO PREVENTIVA E CORRETIVA, COMPREENDENDO OU NÃO O FORNECIMENTO DE PEÇAS E ACESSÓRIOS GENUÍNOS OU ORIGINAIS DE FÁBRICA, CONFORME CONDIÇÕES E ESPECIFICAÇÕES CONTIDAS NESTE TERMO DE REFERÊNCIA.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>31/12/2025 09:00</t>
+          <t>31/12/2025 23:59</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>000004/2025</t>
+          <t>006/2025</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -621,29 +621,29 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE SAO JOAO DO MANTENINHA</t>
+          <t>CONSORCIO INTERMUNICIPAL DE INFRAESTRUTURA DOS MUNICIPIOS DA AMAJE (CII-AMAJE)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NO FORNECIMENTO DE REFEIÇÕES PRONTAS, SENDO ELAS NO MODELO SELF-SERVICE, PRATO FEITO E MARMITEX, PARA ATENDIMENTO DA DEMANDA DE TODAS AS SECRETARIAS DO MUNICÍPIO DE SÃO JOÃO DO MANTENINHA-MG</t>
+          <t xml:space="preserve">CREDENCIAMENTO DE EMPRESAS E PESSOAS FÍSICAS PARA INTEGRAR O CADASTRO DE PRESTADORES DE SERVIÇOS MECÂNICOS, BEM COMO SERVIÇOS DE SOLDA, TORNEARIA E RECUPERAÇÃO DE PEÇAS, OBJETIVANDO ATENDER A DEMANDA COM MANUTENÇÃO PREVENTIVA E CORRETIVA EM ATENDIMENTO AS NECESSIDADES DOS DO CIM JEQUITINHONHA. </t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22705248000190-002</t>
+          <t>113</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>31/12/2025 15:00</t>
+          <t>31/12/2025 23:59</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>19 | Processo 41/2025</t>
+          <t>005/2025</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -653,61 +653,61 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE CATAS ALTAS</t>
+          <t>CONVALES - CONSORCIO DE SAUDE E DESENVOLVIMENTO DOS VALES DO NOROESTE DE MINAS</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>CREDENCIAMENTO POR CHAMADA PUBLICA PARA AQUISICAO DE GENEROS ALIMENTICIOS PERECIVEIS  HORTIFRUTI  CAFE E QUITANDAS  PROVENIENTES DA AGRICULTURA FAMILIAR E OU EMPREENDEDOR FAMILIAR RURAL DE FORMA PARCELADA  DESTINADOS A PREPARACAO E DISTRIBUICAO DA MERENDA ESCOLAR DENTRO DO PROGRAMA NACIONAL DE ALIMENTACAO ESCOLAR   PNAE  NAS UNIDADES ESCOLARES MUNICIPAIS  CONFORME A DEMANDA FUTURA E INCERTA DA SECRETARIA MUNICIPAL DE EDUCACAO  EDITAL E SEUS ANEXOS.</t>
+          <t>CREDENCIAMENTO DE PESSOAS JURÍDICAS PARA FUTURA E EVENTUAL PRESTAÇÃO DE SERVIÇOS MECÂNICOS EM GERAL, MÃO DE OBRA (HORA/TRABALHADA) PARA MANUTENÇÃO PREVENTIVA E CORRETIVA COM APLICAÇÃO E FORNECIMENTO DE PEÇAS E ACESSÓRIOS PARA MANUTENÇÃO DA FROTA DE VEÍCULOS, ÔNIBUS E MOTOS DO CONSÓRCIO DE DESENVOLVIMENTO E VALORIZAÇÃO DOS MUNICÍPIOS – CONVALES, CONFORME CONDIÇÕES ESTABELECIDAS NESTE EDITAL E SEUS ANEXOS.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0000</t>
+          <t>122</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>31/12/2025 16:00</t>
+          <t>05/01/2026 08:00</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>80/2025</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Credenciamento</t>
+          <t>2/2026</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Dispensa</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE OLARIA</t>
+          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES PUBLICOS DO MUNICIPIO DE UBERLANDIA - IPREMU</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>CREDENCIAMENTO DE EMPRESA, RESTAURANTES/CANTINAS, PARA O FORNECIMENTO DE "REFEIÇÕES (SELF SERVICE) E MARMITEX", CONFORME CONDIÇÕES E ESPECIFICAÇÕES CONTIDAS NO TERMO DE REFERÊNCIA - ANEXO I.</t>
+          <t>AQUISIÇÃO DE PEÇAS DE ELEVADOR</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33456</t>
+          <t>929301</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>31/12/2025 17:00</t>
+          <t>05/01/2026 08:01</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>CRE 6/2025</t>
+          <t>CRE 116/2025</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -717,221 +717,221 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE BELO ORIENTE</t>
+          <t>MUNICIPIO DE CLAUDIO</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>CREDENCIAMENTO PARA A PRESTAÇÃO DE SERVIÇOS DE FORNECIMENTO DE REFEIÇÕES A QUILO, MARMITEX E HOSPEDAGEM DESTINADO A ATENDER ÀS NECESSIDADES DE SERVIDORES PÚBLICOS, PRESTADORES DE SERVIÇOS, PARTICIPANTES DE EVENTOS MUNICIPAIS, MEMBROS DA POLÍCIA CIVIL/MILITAR EM OPERAÇÕES EVENTUAIS, E/OU OUTRAS PESSOAS AUTORIZADAS POR CONVÊNIOS E CONTRATOS, GARANTINDO REFEIÇÕES BALANCEADAS, NUTRITIVAS E DE QUALIDADE.</t>
+          <t>CREDENCIAMENTO DE PESSOA JURÍDICA PARA A REALIZAÇÃO DE MANUTENÇÃO CORRETIVA E PREVENTIVA DE CONSULTÓRIO ODONTOLÓGICO, COM PEÇAS INCLUSAS, SE NECESSÁRIO, ALÉM DE INSTALAÇÃO, MONTAGEM E DESMONTAGEM DE EQUIPAMENTOS ODONTOLÓGICOS, CONFORME CONDIÇÕES E ESPECIFICAÇÕES CONTIDAS NO TERMO DE REFERÊNCIA - ANEXO I.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>31/12/2025 23:59</t>
+          <t>05/01/2026 08:30</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>3/2025</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Credenciamento</t>
+          <t>102/2025</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE MARTINHO CAMPOS</t>
+          <t>FUNDACAO HOSPITALAR DO MUNICIPIO DE VARGINHA FHOMUV</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>CREDENCIAMENTO DE EMPRESAS ESPECIALIZADAS NO FORNECIMENTO DE REFEIÇÕES TIPO MARMITEX PARA ATENDER ÀS DEMANDAS DAS SECRETARIAS DE SAÚDE, DESENVOLVIMENTO SOCIAL, CULTURA, ESPORTE, LAZER E TURISMO, ADMINISTRAÇÃO E AGROPECUÁRIA, MEIO AMBIENTE, INDÚSTRIA E COMÉRCIO DO MUNICÍPIO DE MARTINHO CAMPOS.</t>
+          <t>[PORTAL DE COMPRAS PÚBLICAS] - CONTRATAÇÃO DE SERVIÇOS ESPECIALIZADOS DE MANUTENÇÃO PREVENTIVA E CORRETIVA EM SISTEMAS DE COMBATE E PREVENÇÃO A INCÊNDIO, INCLUINDO SERVIÇOS DE REMOÇÃO, INSTALAÇÃO, PINTURA, RECARGA, SUBSTITUIÇÃO DE PEÇAS E REALIZAÇÃO DE TESTE HIDROSTÁTICO EM EXTINTORES E HIDRANTES DA FUNDAÇÃO</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>5920</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>31/12/2025 23:59</t>
+          <t>05/01/2026 10:00</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>1/2025</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Credenciamento</t>
+          <t>90082/2025</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE FELICIO DOS SANTOS</t>
+          <t>MUNICIPIO DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>CREDENCIAMENTO DE EMPRESAS CLASSIFICADAS COMO HOTEL POUSADA E RESTAURANTES PARA A PRESTACAO CONTINUA DE SERVICOS DE FORNECIMENTOS DE REFEICOES A QUILO MARMITEX E HOSPEDAGEM LOCALIZADAS NO MUNICIPIO DE FELICIO DOS SANTOS</t>
+          <t xml:space="preserve">CONTRATAÇÃO DE SERVIÇO DE IMPRESSÃO, REPROGRAFIA E CESSÃO DE EQUIPAMENTOS DE IMPRESSÃO, COMPREENDENDO O DIREITO DO USO GRATUITO DE EQUIPAMENTOS, A INSTALAÇÃO, A CONFIGURAÇÃO, A MANUTENÇÃO (PREVENTIVA E CORRETIVA) E A OPERAÇÃO DOS EQUIPAMENTOS E SISTEMAS APLICADOS NOS SERVIÇOS, O SUPORTE TÉCNICO, A REPOSIÇÃO DE PEÇAS E INSUMOS, EXCETO PAPEL, E OS SERVIÇOS DE GERENCIAMENTO DA PRODUÇÃO CONFORME CONDIÇÕES E EXIGÊNCIAS ESTABELECIDAS NO EDITAL E SEUS ANEXOS. </t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>984123</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>31/12/2025 23:59</t>
+          <t>05/01/2026 13:00</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>000004/2025</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Credenciamento</t>
+          <t>82/2025</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE SAO JOAO DO MANTENINHA</t>
+          <t>MUNICIPIO DE CORONEL FABRICIANO</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NO FORNECIMENTO DE REFEIÇÕES PRONTAS, SENDO ELAS NO MODELO SELF-SERVICE, PRATO FEITO E MARMITEX, PARA ATENDIMENTO DA DEMANDA DE TODAS AS SECRETARIAS DO MUNICÍPIO DE SÃO JOÃO DO MANTENINHA-MG</t>
+          <t>CONTRATAÇÃO DE EMPRESA, PARA FUTURA E EVENTUAL PRESTAÇÃO DE SERVIÇOS DE IMPRESSÃO E REPROGRAFIA, INCLUINDO SOFTWARE DE GESTÃO DE IMPRESSÃO, PLOTAGEM, ENCADERNAÇÃO E PLASTIFICAÇÃO, POR MEIO DO FORNECIMENTO, EM REGIME DE COMODATO DE EQUIPAMENTOS NOVOS (DE PRIMEIRO USO), SENDO IMPRESSORAS E COPIADORAS LED/LASER MONOCROMÁTICAS E POLICROMÁTICAS, MULTIFUNCIONAIS E PLOTTER, COM CAPACIDADE DE IMPRESSÃO DE ATÉ O FORMATO A0, COM MANUTENÇÃO PREVENTIVA E CORRETIVA, ASSISTÊNCIA TÉCNICA ON-SITE, REPOSIÇÃO DE PEÇAS E FORNECIMENTO INTEGRAL DE INSUMOS (INCLUINDO PAPEL E TONER), PARA ATENDER A TODAS AS SECRETARIAS DE GOVERNANÇA  E DEMAIS ÓRGÃOS DA PREFEITURA MUNICIPAL DE CORONEL FABRICIANO, TENDO COMO FONTE DE RECEITA, RECURSOS NÃO VINCULADOS DE IMPOSTOS .</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>301</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>31/12/2025 23:59</t>
+          <t>06/01/2026 08:59</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>0008/2025</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Credenciamento</t>
+          <t>37/2025</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE ITAMARANDIBA</t>
+          <t>MUNICIPIO DE TIMOTEO</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>CREDENCIAMENTO VISANDO O FORNECIMENTO DE SERVIÇOS DE HOSPEDAGENS E FORNECIMENTO DE REFEIÇÕES E MARMITEX PARA ATENDERAS DIVERSAS DEMANDAS MUNICIPAIS</t>
+          <t xml:space="preserve">PREGÃO ELETRÔNICO PARA REGISTRO DE PREÇOS – MAIOR PERCENTUAL DE DESCONTO, CUJO OBJETO É A CONTRATAÇÃO DE SERVIÇOS DE MANUTENÇÃO MECÂNICA, ELÉTRICA / ELETRÔNICA, PREVENTIVA E CORRETIVA COM FORNECIMENTO DE PEÇAS, COMPONENTES E ACESSÓRIOS ORIGINAIS, COM MAIOR PERCENTUAL DE DESCONTO SOBRE TABELA DE REFERÊNCIA CILIA / AUDATEX EM VEÍCULOS LEVES, MÉDIOS E MOTOCICLETAS, CONFORME CONDIÇÕES, QUANTIDADES E EXIGÊNCIAS ESTABELECIDAS NO EDITAL E SEUS ANEXOS. </t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>2442</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>31/12/2025 23:59</t>
+          <t>06/01/2026 09:29</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>000002/2025</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Credenciamento</t>
+          <t>84-2025R/2025</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE CONGONHAS DO NORTE</t>
+          <t>MUNICIPIO DE IAPU</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>CREDENCAMENTO VISANDO A CONTRATAÇÃO DE SERVIÇOS DE FORNECIMENTO DE REFEIÇÕES A KG, MARMITEX E HOSPEDAGEM DO MUNICÍPIO DE CONGONHAS DO NORTE</t>
+          <t>REGISTRO DE PREÇOS PARA FUTURAS E EVENTUAIS PRESTAÇÃO DE SERVIÇOS DE ENGENHARIA, SOB DEMANDA, NÃO CONTÍNUOS, SEM DEDICAÇÃO DE MÃO DE OBRA EXCLUSIVA, COM FORNECIMENTO DE MATERIAIS, PEÇAS, INSUMOS, FERRAMENTAS, MÃO DE OBRAS E DEMAIS RECURSOS NECESSÁRIOS E ADEQUADOS A CORRETA E COMPLETA EXECUÇÃO DOS SERVIÇOS, TENDO COMO BASE PREÇOS DA TABELA SINAPI/MG VIGENTE, CONFORME TERMO DE REFERÊNCIA.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18303180000146-001</t>
+          <t>2336</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>31/12/2025 23:59</t>
+          <t>07/01/2026 08:30</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>01/2025</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Credenciamento</t>
+          <t>194/2025</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE BIQUINHAS</t>
+          <t>MUNICIPIO DE SETE LAGOAS</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE ESTABELECIMENTOS COMERCIAIS INTERESSADOS, MEDIANTE CREDENCIAMENTO, NA PREPARAÇÃO E DISTRIBUIÇÃO DE ALIMENTOS NO SISTEMA REFEIÇÕES TIPO MARMITEX COMERCIAL E SELF-SERVICE, ÁGUA, REFRIGERANTES E SUCOS, PARA ATENDER AS NECESSIDADES DAS SECRETARIAS E ÓRGÃOS MUNICIPAIS DE BIQUINHAS/MG</t>
+          <t>EVENTUAL CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE MANUTENÇÃO PREDIAL PREVENTIVA E CORRETIVA COM FORNECIMENTO DE MATERIAIS, ESTRUTURAS, PEÇAS E MAQUINÁRIOS NECESSÁRIOS AO ATENDIMENTO DAS DEMANDAS DA SME CONFORME CONDIÇÕES E EXIGÊNCIAS ESTABELECIDAS NO DOCUMENTO DE FORMALIZAÇÃO DE DEMANDA - DFD, ESTUDO TÉCNICO PRELIMINAR ELABORADOS PELA SECRETARIA REQUISITANTE E DEMAIS SECRETARIAS QUE MANIFESTARAM INTERESSE EM PARTICIPAR DO PROCESSO.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>111</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>07/01/2026 08:30</t>
+          <t>07/01/2026 08:31</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>98 | Processo 341/2025</t>
+          <t>80/2025</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -941,29 +941,29 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE UBA</t>
+          <t>MUNICIPIO DE FORMIGA</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  REGISTRO DE PRECO PARA FUTURA E EVENTUAL AQUISICAO DE GENEROS ALIMENTICIOS DO TIPO LANCHES  PRONTOS PARA FORNECIMENTO EM CURSOS  TREINAMENTOS  EVENTOS  PALESTRAS E REUNIOES PROMOVIDOS  PELAS SECRETARIAS MUNICIPAIS DE  SAUDE  ADMINISTRACAO  PLANEJAMENTO E DESENVOLVIMENTO  SUSTENTAVEL  CULTURA TURISMO E LAZER  EDUCACAO  DESENVOLVIMENTO SOCIAL  GABINETE DO PREFEITO   ASSESSORIA DE COMUNICACAO  E SEGURANCA PUBLICA E PARA OS USUARIOS QUE FAZEM TRATAMENTOS NOS  DISPOSITIVOS DA RAPS  REDE DE ATENCAO PSICOSSOCIAL   CONFORME ESPECIFICACOES E QUANTITATIVOS  ESTABELECIDOS NESTE DOCUMENTO.</t>
+          <t>[LICITANET] - CONTRATAÇÃO EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇOSDE CÓPIAS E IMPRESSÕES COM FORNECIMENTO DE MÁQUINASMULTIFUNCIONAIS, PEÇAS, COMPONENTES E MATERIAIS DE CONSUMONECESSÁRIOS À SUA MANUTENÇÃO (EXCETO PAPEL), INCLUINDO MANUTENÇÃO PREVENTIVA E CORRETIVA E SOFTWARE DE BILHETAGEM PARA ATENDER AS SECRETARIAS E ÓRGÃOS MUNICIPAIS, BEM COMO ÀS DEMANDAS DECORRENTES DOS CONVÊNIOS FIRMADOS PELO MUNICÍPIO DE FORMIGA.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0000</t>
+          <t>185</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>07/01/2026 12:30</t>
+          <t>07/01/2026 09:30</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>90078/2025</t>
+          <t>45/2025</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -973,29 +973,29 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE PERDOES</t>
+          <t>CIA DE TECNOLOGIA DA INFORMACAO DO ESTADO DE MG</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>REGISTRO DE PREÇOS PARA AQUISIÇÃO DE GÊNEROS ALIMENTÍCIOS HORTIFRUTIGRANJEIROS, DEVIDAMENTE SELECIONADOS, LIMPOS E ACONDICIONADOS CONFORME PADRÕES DE QUALIDADE, HIGIENE E SEGURANÇA ALIMENTAR, DESTINADOS AO ATENDIMENTO DAS DEMANDAS DA SECRETARIA MUNICIPAL DE EDUCAÇÃO (ESCOLAS) E DEMAIS UNIDADES ADMINISTRATIVAS DO MUNICÍPIO DE PERDÕES – MG</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE SUPORTE TÉCNICO COM TROCA DE PEÇAS E ATUALIZAÇÃO DE SOFTWARE PARA O EQUIPAMENTO STORAGE HITACHI VSP (VIRTUAL STORAGE PLATFORM), MODELO G900 NÚMERO DE SÉRIE 448003.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>984997</t>
+          <t>5141001</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>08/01/2026 08:00</t>
+          <t>08/01/2026 07:59</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>032/2025</t>
+          <t>144/2025/2025</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -1005,29 +1005,29 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE MONTE AZUL</t>
+          <t>MUNICIPIO DE LONTRA</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>[PORTAL DE COMPRAS PÚBLICAS] - CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS CONTINUADOS COM FORNECIMENTO DE REFEIÇÕES, DO TIPO SELF SERVICE E MARMITEX, NA CIDADE DE MONTE AZUL - MG.</t>
+          <t>[PORTAL DE COMPRAS PÚBLICAS] - CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS DE LOCAÇÃO DE  VEÍCULOS MÉDIOS, PESADOS E MÁQUINAS FORAS DE ESTRADA, INCLUINDO MANUTENÇÃO PREVENTIVA E CORRETIVA COM A REPOSIÇÃO DE PEÇAS, PARA ATENDER AS NECESSIDADES DAS DIVERSAS SERETARIAS DO MUNICÍPIO DE LONTRA/MG.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5738</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>09/01/2026 08:30</t>
+          <t>08/01/2026 08:59</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>000061/2025</t>
+          <t>70/2025</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -1037,29 +1037,29 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE GUANHAES</t>
+          <t>MUNICIPIO DE JEQUITAI</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>REGISTRO DE PREÇOS PARA FUTURAS E EVENTUAIS AQUISIÇÕES DE DE REFEIÇÕES PRONTAS TIPO MARMITEX E REFEIÇÕES COMPLETAS TIPO SELF-SERVICE ( SERVIÇO NO RESTAURANTE), PARA ATENDER AS DEMANDAS DAS SECRETARIAS MUNICIPAIS E CONVENIADOS.</t>
+          <t>[PORTAL DE COMPRAS PÚBLICAS] - REGISTRO DE PREÇOS PARA EVENTUAL CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA EXECUÇÃO DE SERVIÇOS DE MANUTENÇÃO CORRETIVA EM BOMBAS DE POÇOS ARTESIANOS, BEM COMO O FORNECIMENTO DE PEÇAS E COMPONENTES, DESTINADOS AO ATENDIMENTO DAS NECESSIDADES OPERACIONAIS DE ABASTECIMENTO DE ÁGUA DO MUNICÍPIO DE JEQUITAÍ.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>09/01/2026 09:00</t>
+          <t>08/01/2026 10:00</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>90180/2025</t>
+          <t>23/2025</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -1069,29 +1069,29 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE MONTES CLAROS</t>
+          <t>CONSORCIO PUBLICO INTERMUNICIPAL DE SAUDE DA REDE DE URGENCIA E EMERGENCIA DA MACRORREGIAO DO TRIANGULO DO SUL - CISTRISUL</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">REGISTRO DE PREÇO PARA FUTURA E EVENTUAL CONTRATAÇÃO DE SOCIEDADE EMPRESÁRIA OU UNIPESSOAL PARA FORNECIMENTO DE REFEIÇÕES PRONTAS (MARMITEX) PARA ATENDER A DEMANDA DA SECRETARIA MUNICIPAL DE SAÚDE DO MUNICÍPIO DE MONTES CLAROS - MG. </t>
+          <t>[LICITANET] - CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇOS DE LOCAÇÃO E INSTALAÇÃO DE IMPRESSORAS, INCLUSO ASSISTÊNCIA TÉCNICA COM MANUTENÇÃO PREVENTIVA E CORRETIVA, REPOSIÇÃO DE PEÇAS E FORNECIMENTO DE MATERIAL DE CONSUMO (EXCETO PAPEL).</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>984865</t>
+          <t>2768</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>09/01/2026 09:00</t>
+          <t>08/01/2026 13:30</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>22/2025</t>
+          <t>27/2025</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -1101,81 +1101,721 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE VERISSIMO</t>
+          <t>MUNICIPIO DE NOVA ERA</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>[LICITANET] - AQUISIÇÃO DE HORTIFRUTIGRANJEIROS PARA ATENDER AS NECESSIDADES DA MERENDAR ESCOLAR E SECRETARIA MUNICIPAL DE ASSISTÊNCIA SOCIAL, ATÉ 31 DE DEZEMBRO DE 2026, CONFORME ENTREGA DE REQUISIÇÃO</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM COMUNICAÇÃO INSTITUCIONAL, PARA PRESTAÇÃO DESSERVIÇOS CONTÍNUOS DE DESENVOLVIMENTO DE PEÇAS GRÁFICAS, PRODUÇÃO DE CONTEÚDO AUDIOVISUAL, ASSESSORIA EM MÍDIAS DIGITAIS E APOIO À COMUNICAÇÃO PÚBLICA, COM O OBJETIVO DE PROMOVER ADIVULGAÇÃO DAS AÇÕES, PROGRAMAS, CAMPANHAS E PROJETOS OFICIAIS DO MUNICÍPIO DE NOVA ERA –MG, DE FORMA PADRONIZADA, ÉTICA E EFICIENTE.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>513</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>13/01/2026 08:29</t>
+          <t>08/01/2026 23:59</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>97/2025</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Pregão - Eletrônico</t>
+          <t>001/2025</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Credenciamento</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE PEDRA BONITA</t>
+          <t>CONSORCIO INTERMUNICIPAL MULTIFINALITARIO DA AMAG</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>REGISTRO DE PRECOS PARA FUTURA E EVENTUAL AQUISICAO DE GENEROS ALIMENTICIOS, MATERIAIS DE CONSUMO, MATERIAIS DE LIMPEZA, MATERIAIS PLASTICOS, UTENSILIOS DE COZINHA, PRODUTOS DESCARTAVEIS, MATERIAIS TEXTEIS E CORRELATOS, CONFORME ESPECIFICACOES CONSTANTES NO TERMO DE REFERENCIA, EM ATENDIMENTO AS NECESSIDADES DA SECRETARIA MUNICIPAL DE EDUCACAO DE PEDRA BONITA/MG</t>
+          <t>CREDENCIAMENTO PARA PRESTAÇÃO DE SERVIÇOS ESPECIALIZADOS NA ÁREA DE TECNOLOGIA DA INFORMAÇÃO (TI) , COMPREENDENDO SUPORTE TÉCNICO PRESENCIAL DE MANUTENÇÃO DE MICROS, NOTEBOOKS, IMPRESSORAS E SCANNERS, SEM FORNECIMENTO DE PEÇAS, PARA ATENDER OS EQUIPAMENTOS DE INFORMÁTICA FORA DE GARANTIA E OS QUE  VIEREM A SAIR, AOS USUÁRIOS DE SOLUÇÕES DE TI, SEGUNDO CARACTERÍSTICAS, CONDIÇÕES, OBRIGAÇÕES E REQUISITOS TÉCNICOS DO EDITAL E DE SEUS ANEXOS  PARA  FUTUROS CONTRATOS A SEREM FIRMADOS COM OS 25 (VINTE E CINCO) MUNICÍPIOS DO CONSÓRCIO PÚBLICO CIMAG.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>02007001</t>
+          <t>668</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>09/01/2026 08:00</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>43/2025</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE NOVO CRUZEIRO</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PREÇOS PARA A FUTURA E EVENTUAL CONTRATAÇÃO DE SERVIÇOS COMUNS DE ENGENHARIA PELO TIPO MAIOR DESCONTO SOBRE TABELAS SINAPI E SICOR, OBJETIVANDO CONSTRUÇÃO, REFORMA, AMPLIAÇÃO E MANUTENÇÃO PREDIAL E DE VIAS PÚBLICAS, COM FORNECIMENTO DE EQUIPAMENTOS, MÁQUINAS, PEÇAS, MATERIAIS E MÃO DE OBRA DE ACORDO DEMANDA DO MUNICÍPIO DE NOVO CRUZEIRO – MG</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>09/01/2026 08:45</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>99/2025</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>COMPANHIA OPERACIONAL DE DESENVOLVIMENTO, SANEAMENTO E ACOES URBANAS - CODAU.</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇOS DE MANUTENÇÃO CORRETIVA, COM FORNECIMENTO DE MÃO DE OBRA, INSUMOS, ACESSÓRIOS E PEÇAS DE REPOSIÇÃO, EM PENEIRA DE CANAL ROTATIVA, MOD. PCP-800, UTILIZADA NA ESTAÇÃO DE TRATAMENTO DE ESGOTO (ETE FILOMENA CARTAFINA), UNIDADE PERTENCENTE À CODAU, CONFORME ESPECIFICAÇÕES CONTIDAS NO TERMO DE REFERÊNCIA, EM ATENDIMENTO À SOLICITAÇÃO DA GERÊNCIA DE MANUTENÇÃO ELETROMECÂNICA E AUTOMAÇÃO E DIRETORIA DE DESENVOLVIMENTO E SANEAMENTO.</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>09/01/2026 08:45</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>100/2025</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>COMPANHIA OPERACIONAL DE DESENVOLVIMENTO, SANEAMENTO E ACOES URBANAS - CODAU.</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA FORNECIMENTO DE TUBOS E PEÇAS ESPECIAIS FABRICADOS EM AÇO CARBONO, FIXANDO DIRETRIZES E PROCEDIMENTOS BÁSICOS A SEREM OBSERVADOS NA FABRICAÇÃO, EXECUÇÃO DE TESTES NA FÁBRICA, EMBALAGEM E TRANSPORTE, INCLUINDO AINDA O FORNECIMENTO DE GARANTIAS DE FABRICAÇÃO E DESEMPENHO DE TUBOS E PEÇAS FABRICADOS PARA APLICAÇÃO NA OBRA DO SISTEMA DE ABASTECIMENTO RIO GRANDE DA CODAU, LOCALIZADA EM UBERABA/MG, EM ATENDIMENTO À SOLICITAÇÃO DA DIRETORIA DE DESENVOLVIMENTO E</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>09/01/2026 08:59</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>54/2026</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE BRASOPOLIS</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PREÇO PARA FUTURA E EVENTUAL CONTRATAÇÃO DE EMPRESA PARA A AQUISIÇÃO DE PEÇAS VEICULARES E ACESSÓRIOS AUTOMOTIVOS GENUÍNOS OU ORIGINAIS COM MAIOR DESCONTO NA TABELA DA MONTADORA, EM ATENDIMENTO A DIVISÃO DE TRANSPORTE E MANUTENÇÃO, CONFORME DESCRIÇÕES NO TERMO DE REFERENCIA.</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>09/01/2026 08:59</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>62/2025</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE RIBEIRAO DAS NEVES</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇO DE MANUTENÇÃO PREVENTIVA E CORRETIVA COM REPOSIÇÃO DE PEÇAS PARA ELEVADOR DO HOSPITAL MUNICIPAL SÃO JUDAS TADEU </t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>835</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>09/01/2026 09:00</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>41/2025</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>CISMEV CONSORCIO INTERMU DE SAUDE DO M RIO DAS VELHAS</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>CONTRATAÇÃO DO SERVIÇO DE MANUTENÇÃO EM ASPERSORES COSTAIS PORTÁTEIS DE UBV, COM O FORNECIMENTO DE PEÇAS.</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>09/01/2026 09:30</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>5/2025</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A. - BDMG</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>SERVIÇOS CONTINUADOS DE OPERAÇÃO E MANUTENÇÃO PREVENTIVA E CORRETIVA, SEM FORNECIMENTO DE PEÇAS, DO SISTEMA DE CLIMATIZAÇÃO E EXAUSTÃO DE AR DO BDMG, CONFORME ESPECIFICAÇÕES DO EDITAL.</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>5201014</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>12/01/2026 08:30</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>46/2025</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE PAI PEDRO</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>AQUISIÇÃO  PARCELADA DE PEÇAS E OUTROS CORRELATOS DE MOTOCICLETAS HONDA PARA ATENDER AS SECRETARIAS DESTA MUNICIPALIDADE.</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>711</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>12/01/2026 08:59</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>46/2025RET2/2025</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE PARACATU</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PREÇOS PARA FUTURA E EVENTUAL CONTRATAÇÃO DE  EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇOS CONTÍNUOS EM  MANUTENÇÃO PREVENTIVA E CORRETIVA COM FORNECIMENTO DE PEÇAS PARA  EQUIPAMENTOS AUTOCLAVES INSTALADAS NAS UNIDADES DE SAÚDE DO MUNICÍPIO</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>2178</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>12/01/2026 09:00</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>137/2025</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE PARACATU</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PREÇOS PARA FUTURA E EVENTUAL CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇOS CONTÍNUOS EM MANUTENÇÃO PREVENTIVA E CORRETIVA COM FORNECIMENTO DE PEÇAS PARA EQUIPAMENTOS AUTOCLAVES NAS UNIDADES DE SAÚDE DO MUNICÍPIO DE PARACATU-MG.</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>020601</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>12/01/2026 09:00</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>056/2025</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>SUPERINTENDENCIA DE AGUA E ESGOTOS DE ITUIUTABA</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>[LICITANET] - CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇOS DE MANUTENÇÃO PREVENTIVA E CORRETIVA NA MÁQUINA M22 PLUS ENVASADORA DE COPOS DA SAE, INCLUINDO FORNECIMENTO DE MÃO DE OBRA, PEÇAS E MATERIAIS DE REPOSIÇÃO, PARA O PERÍODO DE 12 (DOZE) MESES, CONFORME ESPECIFICAÇÕES, QUANTIDADES E CONDIÇÕES DE EXECUÇÃO CONSTANTES DO ANEXO I - TERMO DE REFERÊNCIA.</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>1734</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>12/01/2026 10:15</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>128/2025</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE LAVRAS</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>[PORTAL DE COMPRAS PÚBLICAS] - REGISTRO DE PREÇOS PARA FUTURA E EVENTUAL CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE MANUTENÇÃO PREVENTIVA E CORRETIVA DO SISTEMA DE EXAUSTÃO, INCLUINDO INSPEÇÃO, LIMPEZA, CALIBRAÇÃO, TESTE DE VAZÃO DE AR, VERIFICAÇÃO DE SELAGEM, AJUSTES MECÂNICOS E ELÉTRICOS, E SUBSTITUIÇÃO DE PEÇAS/ACESSÓRIOS.</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>5641</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>13/01/2026 08:30</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>083/2025</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE ALFENAS</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>[PORTAL DE COMPRAS PÚBLICAS] - CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA LOCAÇÃO DE EQUIPAMENTOS NOBREAKS DE FORNECIMENTO DE ENERGIA ININTERRUPTA, INCLUINDO SERVIÇOS DE MANUTENÇÃO PREVENTIVA E CORRETIVA COM FORNECIMENTO DE PEÇAS E BATERIAS INCLUSAS, EQUIPAMENTOS NOVOS, PRIMEIRO USO.</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>3932</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
           <t>13/01/2026 08:59</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>47/2025</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Pregão - Eletrônico</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>MUNICIPIO DE BETIM</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>[PORTAL DE COMPRAS PÚBLICAS] - GÊNEROS ALIMENTÍCIOS - HORTIFRUTIGRANJEIROS CONVENCIONAL, PARA ATENDIMENTO AO PROGRAMA NACIONAL DE ALIMENTAÇÃO ESCOLAR, NO ÂMBITO DO MUNICÍPIO DE BETIM-MG.</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>48/2025</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE RIBEIRAO DAS NEVES</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>CONTRATAÇÃO DA PRESTAÇÃO DE SERVIÇOS DE LOCAÇÃO DE GRUPO GERADOR INSTALADO, COM MANUTENÇÃO PREVENTIVA, CORRETIVA, COM REPOSIÇÃO DE PEÇAS, INSUMOS E COMBUSTÍVEL PARA A UPA JOANICO CIRILO DE ABREU E O CENTRO ESTADUAL DE ATENÇÃO ESPECIALIZADA – CEAE.</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>835</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>13/01/2026 08:59</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>18/2025SAU/2025</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE PARACATU</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS CONTÍNUOS DE MANUTENÇÃO PREVENTIVA E CORRETIVA COM FORNECIMENTO DE PEÇAS PARA APARELHO DE TOMOGRAFIA DA MARCA SIEMENS LOTADO NO HOSPITAL MUNICIPAL DE PARACATU-MG</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>2178</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>13/01/2026 22:59</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>PL-166/2025</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE PARACATU</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA A PRESTAÇÃO DE SERVIÇOS CONTÍNUOS DE MANUTENÇÃO PREVENTIVA E CORRETIVA COM FORNECIMENTO DE PEÇAS PARA APARELHO DE TOMOGRAFIA DA MARCA SIEMENS LOTADO NO HOSPITAL MUNICIPAL DE PARACATU-MG. </t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>020601</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>14/01/2026 08:00</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>90031/2025</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE PIRAPORA</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PREÇOS PARA FUTURA E EVENTUAL CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇO DE MANUTENÇÃO PREVENTIVA E CORRETIVA COM FORNECIMENTO INTEGRAL DE PEÇAS PARA OS ARES CONDICIONADOS, FREEZER, FRIGOBAR, GELADEIRAS, BEBEDOUROS, CORTINAS DE AR E MÁQUINAS DE LAVAR ROUPAS DA PREFEITURA MUNICIPAL DE PIRAPORA-MG/2025</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>985023</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>14/01/2026 08:29</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>00015525/2025</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE VISCONDE DO RIO BRANCO</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>O PRESENTE PROCESSO LICITATÓRIO TEM COMO OBJETO O REGISTRO DE PREÇOS PARA EVENTUAL E FUTURA CONTRATAÇÃO DE SERVIÇOS DE MANUTENÇÃO PREVENTIVA E CORRETIVA, COM FORNECIMENTO INTEGRAL DE PEÇAS E ACESSÓRIOS DO GERADOR DE ENERGIA A DIESEL 33KVA / 72KV, MARCA NAGANO, MODELO ND33100ES3, INSTALADO NO CENTRO DE SAÚDE BEIRA RIO.</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>02001</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>14/01/2026 09:00</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>028/2025/2025</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE PARA DE MINAS</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA PRESTAÇÃO DOS SERVIÇOS DE MANUTENÇÃO PREVENTIVA E CORRETIVA NOS EQUIPAMENTOS E NA ESTRUTURA DO SISTEMA DE VIDEOMONITORAMENTO DA SEGURANÇA PÚBLICA DO MUNICÍPIO DE PARÁ DE MINAS-MG, DENOMINADO “OLHO VIVO”, INCLUINDO SERVIÇOS DE INSTALAÇÕES, DESINSTALAÇÕES, REPARO E ADEQUAÇÃO NA INFRAESTRUTURA APARENTE OU SUBTERRÂNEA, COM FORNECIMENTO E SUBSTITUIÇÃO DE EQUIPAMENTOS, PEÇAS, COMPONENTES, ACESSÓRIOS E MATERIAIS NECESSÁRIOS PARA REPOSIÇÃO, INCLUINDO SUPORTE TÉCNICO E ATUALIZAÇÃO DOS SOFTWARES.</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>14/01/2026 09:00</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>14/2025</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>BETIM CAMARA MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>[PORTAL DE COMPRAS PÚBLICAS] - MANUTENÇÃO PREVENTIVA TRIMESTRAL E CORRETIVA, SOB DEMANDA, DE 85 APARELHOS DE ARCONDICIONADO, DE 10.000 A 60.000 BTU`S, INCLUINDO O FORNECIMENTO DE TODAS AS PEÇAS, INSUMOSE MÃO DE OBRA NECESSÁRIOS PARA A PREVENÇÃO E A CORREÇÃO, EXCETO AS PEÇAS LISTADAS NO ITEM 6.5DESTE DOCUMENTO, AS QUAIS TERÃO SEU VALOR RESSARCIDOS PELA CMB, DESDE QUE COMPROVADANECESSIDADE DE SUBSTITUIÇÃO, RESPEITADO O LIMITE DE R$ 18.500,00 ANUAIS.</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>6452</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>14/01/2026 09:00</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>PE 28/2025</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Pregão - Eletrônico</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE PARA DE MINAS</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA PRESTAÇÃO DOS SERVIÇOS DE MANUTENÇÃO PREVENTIVA E CORRETIVA NOS EQUIPAMENTOS E NA ESTRUTURA DO SISTEMA DE VIDEOMONITORAMENTO DA SEGURANÇA PÚBLICA DO MUNICÍPIO DE PARÁ DE MINAS-MG, DENOMINADO “OLHO VIVO”, INCLUINDO SERVIÇOS DE INSTALAÇÕES, DESINSTALAÇÕES, REPARO E ADEQUAÇÃO NA INFRAESTRUTURA APARENTE OU SUBTERRÂNEA, COM FORNECIMENTO E SUBSTITUIÇÃO DE EQUIPAMENTOS, PEÇAS, COMPONENTES, ACESSÓRIOS E MATERIAIS NECESSÁRIOS PARA REPOSIÇÃO, INCLUINDO SUPORTE TÉCNICO E ATUALIZAÇÃO DOS SOFTWARES.</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>25347</t>
         </is>
       </c>
     </row>
